--- a/05. Res/modelos/comparativo_modelos.xlsx
+++ b/05. Res/modelos/comparativo_modelos.xlsx
@@ -439,22 +439,22 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>3.86543008531065</v>
+        <v>5.59893959151156</v>
       </c>
       <c r="D2" t="n">
-        <v>0.616651499791168</v>
+        <v>0.588230055525235</v>
       </c>
       <c r="E2" t="n">
-        <v>0.409895661205798</v>
+        <v>0.407541492312756</v>
       </c>
       <c r="F2" t="n">
-        <v>0.472140916085514</v>
+        <v>0.443549171725226</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0622452548797168</v>
+        <v>0.0360076794124704</v>
       </c>
       <c r="H2" t="n">
-        <v>125542.160457747</v>
+        <v>126185.133956352</v>
       </c>
     </row>
     <row r="3">
@@ -465,19 +465,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>3.86543008531065</v>
+        <v>5.59893959151156</v>
       </c>
       <c r="D3" t="n">
-        <v>0.616651499791168</v>
+        <v>0.588230055525235</v>
       </c>
       <c r="E3" t="n">
-        <v>0.409895661205798</v>
+        <v>0.407541492312756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.472140916085514</v>
+        <v>0.443549171725226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0622452548797168</v>
+        <v>0.0360076794124704</v>
       </c>
       <c r="H3"/>
     </row>
@@ -489,22 +489,22 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>0.315662090135747</v>
+        <v>0.311455100999126</v>
       </c>
       <c r="D4" t="n">
-        <v>0.193806867451649</v>
+        <v>0.191767787660409</v>
       </c>
       <c r="E4" t="n">
-        <v>0.190548132760493</v>
+        <v>0.186844703559171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.187706975726861</v>
+        <v>0.192360288975075</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.00284115703363204</v>
+        <v>0.0055155854159041</v>
       </c>
       <c r="H4" t="n">
-        <v>53641.4472567833</v>
+        <v>53733.72772426</v>
       </c>
     </row>
     <row r="5">
@@ -515,22 +515,22 @@
         <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>8988.70322892631</v>
+        <v>15158.6825101518</v>
       </c>
       <c r="D5" t="n">
-        <v>1030.13719526887</v>
+        <v>1034.99234549563</v>
       </c>
       <c r="E5" t="n">
-        <v>780.983332507433</v>
+        <v>786.516932561651</v>
       </c>
       <c r="F5" t="n">
-        <v>1070.96150326677</v>
+        <v>1084.44659473087</v>
       </c>
       <c r="G5" t="n">
-        <v>289.978170759332</v>
+        <v>297.929662169218</v>
       </c>
       <c r="H5" t="n">
-        <v>237123.273314962</v>
+        <v>237866.768758652</v>
       </c>
     </row>
     <row r="6">
@@ -541,22 +541,22 @@
         <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>2044.82814361852</v>
+        <v>2253.16607217981</v>
       </c>
       <c r="D6" t="n">
-        <v>671.265425528124</v>
+        <v>662.648543111903</v>
       </c>
       <c r="E6" t="n">
-        <v>780.983332507433</v>
+        <v>786.516932561651</v>
       </c>
       <c r="F6" t="n">
-        <v>344.232626999137</v>
+        <v>338.431242731676</v>
       </c>
       <c r="G6" t="n">
-        <v>-436.750705508296</v>
+        <v>-448.085689829975</v>
       </c>
       <c r="H6" t="n">
-        <v>51516.2484220695</v>
+        <v>51789.4732581988</v>
       </c>
     </row>
   </sheetData>
